--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/hero_banner_size.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/hero_banner_size.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C2" t="n">
-        <v>53.5</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
-        <v>31.5</v>
+        <v>29.91</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>5.36</v>
       </c>
     </row>
   </sheetData>
